--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Downloads/4900/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Documents/GitHub/ENGMT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF48650C-0EFA-0A49-A753-72436F557E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA57B4A-443A-DC41-8C74-1B573173CE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="128">
   <si>
     <t>Term</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>• Each file reads this spreadsheet automatically; if it can't be reached, it falls back to a built-in copy of that module's terms.</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>this is a test</t>
   </si>
 </sst>
 </file>
@@ -457,7 +463,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -480,11 +486,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D6D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D6D0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -502,6 +519,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -806,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
@@ -825,7 +848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>66</v>
       </c>
@@ -1373,6 +1396,17 @@
       </c>
       <c r="C51" s="3" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Documents/GitHub/ENGMT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA57B4A-443A-DC41-8C74-1B573173CE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A57F91-3581-0947-81CB-0F694624741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
   <si>
     <t>Term</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>this is a test</t>
+  </si>
+  <si>
+    <t>test2</t>
   </si>
 </sst>
 </file>
@@ -501,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -519,6 +522,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -829,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
@@ -1407,6 +1416,17 @@
       </c>
       <c r="C52" s="8" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Documents/GitHub/ENGMT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AD75C7-1D0A-8440-872E-D398D8606B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9801D3A7-D073-3E40-8F91-0D99348CD091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="163">
   <si>
     <t>Term</t>
   </si>
@@ -507,6 +507,12 @@
   </si>
   <si>
     <t>Module</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>up test</t>
   </si>
 </sst>
 </file>
@@ -526,23 +532,27 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF303030"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF303030"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFB31B1B"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -565,7 +575,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -588,11 +598,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D6D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D6D0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -614,6 +635,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1693,6 +1720,17 @@
       </c>
       <c r="C70" s="3" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9801D3A7-D073-3E40-8F91-0D99348CD091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AA496C-6876-5248-B775-4B883B5FB81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="161">
   <si>
     <t>Term</t>
   </si>
@@ -507,12 +507,6 @@
   </si>
   <si>
     <t>Module</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>up test</t>
   </si>
 </sst>
 </file>
@@ -636,10 +630,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1723,15 +1717,9 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>4</v>
-      </c>
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C70" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AA496C-6876-5248-B775-4B883B5FB81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817A50E9-F882-3E4E-9CE0-1B7B64171199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="How to use" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glossary!$A$1:$C$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glossary!$A$1:$C$71</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="163">
   <si>
     <t>Term</t>
   </si>
@@ -35,9 +35,6 @@
     <t>'Problem' → 'Challenge/Opportunity' Reframing</t>
   </si>
   <si>
-    <t>A linguistic reframe that shifts team culture from defeatism toward proactive, solution-oriented thinking.</t>
-  </si>
-  <si>
     <t>Module 1</t>
   </si>
   <si>
@@ -507,6 +504,15 @@
   </si>
   <si>
     <t>Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A linguistic reframe that shifts team culture from defeatism toward proactive, solution-oriented thinking. I'm testing uploading a new file. </t>
+  </si>
+  <si>
+    <t>test word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to see that new excel works or not. </t>
   </si>
 </sst>
 </file>
@@ -938,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -954,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -962,767 +968,778 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C41" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C42" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C44" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C45" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C56" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C60" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+      <c r="B61" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C61" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C61" s="3" t="s">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C68" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
+      <c r="C71" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="8"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C70" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1737,7 +1754,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -1745,7 +1762,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
@@ -1753,17 +1770,17 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
@@ -1771,32 +1788,32 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
@@ -1804,22 +1821,22 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817A50E9-F882-3E4E-9CE0-1B7B64171199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EA48DE-C94D-894E-BAAA-445C52736ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="How to use" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glossary!$A$1:$C$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glossary!$A$1:$C$70</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="161">
   <si>
     <t>Term</t>
   </si>
@@ -506,13 +506,7 @@
     <t>Module</t>
   </si>
   <si>
-    <t xml:space="preserve">A linguistic reframe that shifts team culture from defeatism toward proactive, solution-oriented thinking. I'm testing uploading a new file. </t>
-  </si>
-  <si>
-    <t>test word</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I want to see that new excel works or not. </t>
+    <t xml:space="preserve">A linguistic reframe that shifts team culture from defeatism toward proactive, solution-oriented thinking. </t>
   </si>
 </sst>
 </file>
@@ -944,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -974,23 +968,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -998,10 +992,10 @@
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>3</v>
@@ -1009,32 +1003,32 @@
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>3</v>
@@ -1042,54 +1036,54 @@
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>3</v>
@@ -1097,10 +1091,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>3</v>
@@ -1108,10 +1102,10 @@
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>3</v>
@@ -1119,32 +1113,32 @@
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>3</v>
@@ -1152,10 +1146,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>3</v>
@@ -1163,21 +1157,21 @@
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -1185,21 +1179,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>3</v>
@@ -1207,10 +1201,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>3</v>
@@ -1218,10 +1212,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>3</v>
@@ -1229,10 +1223,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>3</v>
@@ -1240,10 +1234,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>3</v>
@@ -1251,10 +1245,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>3</v>
@@ -1262,10 +1256,10 @@
     </row>
     <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>3</v>
@@ -1273,10 +1267,10 @@
     </row>
     <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>3</v>
@@ -1284,32 +1278,32 @@
     </row>
     <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>3</v>
@@ -1317,10 +1311,10 @@
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>3</v>
@@ -1328,10 +1322,10 @@
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>3</v>
@@ -1339,10 +1333,10 @@
     </row>
     <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>3</v>
@@ -1350,109 +1344,109 @@
     </row>
     <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>78</v>
@@ -1460,43 +1454,43 @@
     </row>
     <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>97</v>
@@ -1504,10 +1498,10 @@
     </row>
     <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>97</v>
@@ -1515,10 +1509,10 @@
     </row>
     <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>97</v>
@@ -1526,10 +1520,10 @@
     </row>
     <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>97</v>
@@ -1537,10 +1531,10 @@
     </row>
     <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>97</v>
@@ -1548,32 +1542,32 @@
     </row>
     <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>97</v>
@@ -1581,10 +1575,10 @@
     </row>
     <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>97</v>
@@ -1592,54 +1586,54 @@
     </row>
     <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>127</v>
@@ -1647,10 +1641,10 @@
     </row>
     <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>127</v>
@@ -1658,21 +1652,21 @@
     </row>
     <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>127</v>
@@ -1680,21 +1674,21 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>127</v>
@@ -1702,10 +1696,10 @@
     </row>
     <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>127</v>
@@ -1713,33 +1707,22 @@
     </row>
     <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C70" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ay373/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbtne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EA48DE-C94D-894E-BAAA-445C52736ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BEB573-70FE-4DFF-8AA4-A69CE054C3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26115" yWindow="1140" windowWidth="27510" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Glossary" sheetId="1" r:id="rId1"/>
     <sheet name="How to use" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glossary!$A$1:$C$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glossary!$A$1:$C$65</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="151">
   <si>
     <t>Term</t>
   </si>
@@ -32,42 +32,21 @@
     <t>Definition</t>
   </si>
   <si>
-    <t>'Problem' → 'Challenge/Opportunity' Reframing</t>
-  </si>
-  <si>
     <t>Module 1</t>
   </si>
   <si>
     <t>Amygdala</t>
   </si>
   <si>
-    <t>The brain's threat-detection center in the limbic system; it scans for danger and triggers the fight-flight-freeze response, often before the thinking brain (neocortex) engages. Key to managing emotional reactions under project pressure.</t>
-  </si>
-  <si>
     <t>Amygdala Hijacking</t>
   </si>
   <si>
-    <t>An immediate, overwhelming emotional reaction where the amygdala overrides rational thought; it should be managed and understood, not simply suppressed at all costs.</t>
-  </si>
-  <si>
     <t>ANTS (Automatic Negative Thoughts)</t>
   </si>
   <si>
-    <t>Habitual, involuntary negative interpretations that surface automatically (e.g. 'this will never work,' 'they think I'm incompetent'). Noticing and challenging ANTs is a core emotional self-management skill.</t>
-  </si>
-  <si>
     <t>Breakdown (Emotional Breakdown)</t>
   </si>
   <si>
-    <t>The point at which accumulated stress or a triggering event overwhelms a person's ability to self-regulate, impairing judgment and communication. Anticipating and defusing breakdowns is part of self-management.</t>
-  </si>
-  <si>
-    <t>Cognitive Distortion</t>
-  </si>
-  <si>
-    <t>Irrational or exaggerated thought patterns that skew perception of reality (a Module 2 EI concept).</t>
-  </si>
-  <si>
     <t>Criticism</t>
   </si>
   <si>
@@ -83,93 +62,45 @@
     <t>Dissonant Leaders</t>
   </si>
   <si>
-    <t>Leaders who are out of tune with their team's emotions, creating negativity, tension, and disengagement.</t>
-  </si>
-  <si>
     <t>EI / EQ (Emotional Intelligence)</t>
   </si>
   <si>
-    <t>The ability to recognize, understand, and manage your own emotions and those of others; a core PM skill distinct from IQ — the two are not directly correlated.</t>
-  </si>
-  <si>
     <t>Emotional Reasoning</t>
   </si>
   <si>
-    <t>A cognitive distortion of treating feelings as facts ('I feel it, therefore it's true') despite contrary evidence.</t>
-  </si>
-  <si>
     <t>Emotional Resilience</t>
   </si>
   <si>
-    <t>The capacity to recover quickly from setbacks, stress, and adversity while staying functional and composed — bouncing back rather than being derailed by difficult project events.</t>
-  </si>
-  <si>
     <t>Emotions</t>
   </si>
   <si>
-    <t>Short-lived affective signals (anger, fear, joy, and so on) that carry information about what matters to us. In EI, emotions are data to be understood and managed — not simply suppressed or blindly obeyed.</t>
-  </si>
-  <si>
-    <t>Fourth Critical Concept</t>
-  </si>
-  <si>
-    <t>Rounding out 'vision, mission, goals,' the fourth key concept for PMs discussed in class — the completing pillar of the planning hierarchy.</t>
-  </si>
-  <si>
     <t>Fredrickson's Positive Emotions</t>
   </si>
   <si>
-    <t>Barbara Fredrickson's research identifying ~10 of the most important positive emotions (e.g. joy, gratitude, serenity, interest, hope) that broaden thinking and build resilience.</t>
-  </si>
-  <si>
     <t>Goal</t>
   </si>
   <si>
-    <t>A concrete, actionable target derived from vision/mission.</t>
-  </si>
-  <si>
     <t>Hostility</t>
   </si>
   <si>
-    <t>Overt or veiled aggression — anger, contempt, or antagonism directed at others. A red-flag behavior that damages psychological safety and team cohesion.</t>
-  </si>
-  <si>
     <t>Inappropriate Humor</t>
   </si>
   <si>
-    <t>Jokes, teasing, or sarcasm at others' expense or in tense moments, which can mask hostility, belittle people, or deflect from real issues. A communication red flag.</t>
-  </si>
-  <si>
     <t>IQ (Intelligence Quotient)</t>
   </si>
   <si>
-    <t>A measure of cognitive and analytical intelligence. Distinct from EQ — strong technical IQ does not guarantee the people skills project leadership requires; the two are not directly correlated.</t>
-  </si>
-  <si>
     <t>Limbic Brain</t>
   </si>
   <si>
-    <t>The 'emotional brain': responsible for processing emotions, memory, and social/relational responses.</t>
-  </si>
-  <si>
     <t>Neocortex</t>
   </si>
   <si>
-    <t>The 'thinking brain': responsible for rational thought, reasoning, language, and conscious decision-making.</t>
-  </si>
-  <si>
     <t>Old Brain (Reptilian Brain)</t>
   </si>
   <si>
-    <t>The most primitive brain region: responsible for basic survival functions and instinctual responses (fight-or-flight, breathing, heart rate).</t>
-  </si>
-  <si>
     <t>Passive-Aggressive Behavior</t>
   </si>
   <si>
-    <t>Indirect expression of negative feelings (e.g. silent treatment, backhanded comments, deliberate procrastination) instead of open communication.</t>
-  </si>
-  <si>
     <t>Personality</t>
   </si>
   <si>
@@ -179,21 +110,9 @@
     <t>Playing the Victim</t>
   </si>
   <si>
-    <t>Framing oneself as powerless and blameless so responsibility always lies elsewhere. It avoids accountability and blocks problem-solving; ownership and co-creation are the antidote.</t>
-  </si>
-  <si>
-    <t>Plutchik's Wheel of Emotions</t>
-  </si>
-  <si>
-    <t>Robert Plutchik's model organizing eight primary emotions and their combinations and intensities into a color wheel.</t>
-  </si>
-  <si>
     <t>Pre-thinking</t>
   </si>
   <si>
-    <t>Deliberately pausing to consider the consequences of a decision before acting, so emotions don't drive a reactive choice.</t>
-  </si>
-  <si>
     <t>Project</t>
   </si>
   <si>
@@ -203,15 +122,9 @@
     <t>Prospective Hindsight</t>
   </si>
   <si>
-    <t>Imagining a project has already failed (or succeeded) and reasoning backward to explain why — the basis of a 'pre-mortem.' It surfaces risks and blind spots people otherwise miss.</t>
-  </si>
-  <si>
     <t>Reactivity</t>
   </si>
   <si>
-    <t>Responding automatically and emotionally to a trigger without pause or reflection — the opposite of pre-thinking and emotional self-management.</t>
-  </si>
-  <si>
     <t>Resonant Leaders</t>
   </si>
   <si>
@@ -221,96 +134,45 @@
     <t>Sarcasm</t>
   </si>
   <si>
-    <t>Mocking or ironic remarks that convey criticism or contempt under the cover of humor; a passive form of hostility and a communication red flag.</t>
-  </si>
-  <si>
     <t>Self Confidence</t>
   </si>
   <si>
-    <t>A grounded belief in your own abilities and judgment that lets you act, decide, and lead under uncertainty — without arrogance or a need for constant reassurance.</t>
-  </si>
-  <si>
     <t>Self-Awareness</t>
   </si>
   <si>
-    <t>The foundation of emotional intelligence: accurately recognizing your own emotions, triggers, strengths, limits, and your impact on others in the moment.</t>
-  </si>
-  <si>
     <t>SMART Goal</t>
   </si>
   <si>
-    <t>A goal that is Specific, Measurable, Achievable, Relevant, and Time-bound — applies to everyday and advanced tasks alike.</t>
-  </si>
-  <si>
     <t>Soft Skills</t>
   </si>
   <si>
-    <t>Interpersonal and self-management capabilities — communication, empathy, collaboration, leadership, emotional intelligence — that drive project success as much as technical ('hard') skills.</t>
-  </si>
-  <si>
     <t>Vision vs. Mission</t>
   </si>
   <si>
-    <t>Vision is the desired future state (what/why we aspire to); mission is why and how you'll get there.</t>
-  </si>
-  <si>
-    <t>'Calm Down' Fallacy</t>
-  </si>
-  <si>
-    <t>Telling a visibly tense person to 'calm down' reflects an unhealthy attitude toward emotions and typically backfires.</t>
-  </si>
-  <si>
     <t>Module 2</t>
   </si>
   <si>
     <t>7 Red Flags</t>
   </si>
   <si>
-    <t>A set of warning signs of problematic workplace behavior/communication discussed in class — a specific list to recognize and address early.</t>
-  </si>
-  <si>
     <t>AEIOU (Listening Framework)</t>
   </si>
   <si>
-    <t>A class acronym for active/effective listening — a structured reminder of good listening behaviors.</t>
-  </si>
-  <si>
     <t>Barriers to Effective Listening</t>
   </si>
   <si>
     <t>Obstacles such as distraction, prejudging, formulating your reply while the other person talks, and emotional reactivity.</t>
   </si>
   <si>
-    <t>Conflict-Handling Modes</t>
-  </si>
-  <si>
-    <t>Five approaches from the conflict readings: Collaboration (win-win problem solving), Compromise (mutual give-and-take), Smoothing/Accommodating (emphasizing agreement, downplaying differences), Forcing (asserting your position to win), and Withdrawing/Avoiding (retreating from the conflict).</t>
-  </si>
-  <si>
     <t>Fundamental Attribution Error</t>
   </si>
   <si>
-    <t>The tendency to blame others' failures on their character while attributing our own failures to external circumstances.</t>
-  </si>
-  <si>
     <t>Phubbing</t>
   </si>
   <si>
-    <t>Snubbing someone in a social interaction by paying attention to your phone instead of them.</t>
-  </si>
-  <si>
     <t>Sympathy vs. Empathy</t>
   </si>
   <si>
-    <t>Sympathy is feeling for someone (pity/acknowledgment from a distance); empathy is feeling with them (understanding their perspective from their point of view). Empathy is the more valuable PM skill.</t>
-  </si>
-  <si>
-    <t>Venting (Supportive Response)</t>
-  </si>
-  <si>
-    <t>When someone vents, they first need to feel heard/validated — not an immediate action plan or a redirect to your own similar story.</t>
-  </si>
-  <si>
     <t>'Performing' Stage Pitfall</t>
   </si>
   <si>
@@ -506,27 +368,151 @@
     <t>Module</t>
   </si>
   <si>
-    <t xml:space="preserve">A linguistic reframe that shifts team culture from defeatism toward proactive, solution-oriented thinking. </t>
+    <t>A rapid, intense emotional response in which a perceived threat temporarily narrows attention and reduces access to deliberate reasoning. Effective self-management begins by noticing and regulating our responses and behaviors, rather than simply suppressing it.</t>
+  </si>
+  <si>
+    <t>A pair of structures in the limbic system involved in detecting emotionally significant stimuli, especially potential threats, and rapidly coordinating responses before deliberate reasoning fully engages. The amygdala helps initiate fight, flight, or freeze responses to threats,...whether real, perceived, remembered, or imagined. Understanding this process can help project leaders recognize and manage their reactions under pressure.</t>
+  </si>
+  <si>
+    <t>Why call a Problem an Opportinity or a Challenge?</t>
+  </si>
+  <si>
+    <t>For many people and in many situations, the word “problem” can trigger negative emotions or reinforce feelings of powerlessness and defeat. Reframing a problem as an opportunity or challenge can reduce this negative response and encourage a more constructive, solution-oriented mindset.</t>
+  </si>
+  <si>
+    <t>Habitual, involuntary negative interpretations that arise automatically (e.g., “This will never work” or “They think I’m incompetent” or "this meeting will be more wasted time"). Noticing and challenging ANTs is a core emotional self-management skill.</t>
+  </si>
+  <si>
+    <t>A moment, large or small, when stress, frustration, fear, or another emotional trigger disrupts a person’s ability to respond in the most effectuve manner. Breakdowns can occur frequently and may appear as criticism, sarcasm, withdrawal, withholding information, avoiding responsibility, or failing to speak up. Even small breakdowns can impair performance and judgment and damage trust and relationships. Recognizing and managing them early is an important self-management skill.</t>
+  </si>
+  <si>
+    <t>Cognitive Distortions</t>
+  </si>
+  <si>
+    <t>Habitual, biased patterns of thinking that distort how a person interprets a situation, often leading to inaccurate, exaggerated, or unhelpful conclusions. Examples include personalization, catastrophizing, mind reading, all-or-nothing thinking, and many others.</t>
+  </si>
+  <si>
+    <t>Leaders who are out of tune with their team's emotions, creating negativity, tension, low morale,  and disengagement.</t>
+  </si>
+  <si>
+    <t>The ability to recognize, understand, and manage your own emotions and those of others</t>
+  </si>
+  <si>
+    <t>A cognitive distortion in which a person’s emotional state shapes how they interpret a situation, and the resulting thought or assumption is accepted as an accurate description of reality. For example, feeling anxious and insecure around your boss may lead to the conclusion, “My boss dislikes me,” even though the feeling itself does not reveal what your boss actually thinks.</t>
+  </si>
+  <si>
+    <t>The capacity to recover and adapt after setbacks, stress, or adversity while continuing to function effectively and maintain perspective.</t>
+  </si>
+  <si>
+    <t>Relatively brief psychological and physiological responses (such as anger, fear, or joy) that provide information about what matters to us. In emotional intelligence, emotions are signals to be understood and managed, not simply suppressed or blindly accepted.</t>
+  </si>
+  <si>
+    <t>Barbara Fredrickson's research identifying 10 examples of important positive emotions that broaden thinking and build resilience. (Joy, gratitude, serenity, interest, hope, pride, amusement, inspiration, awe, love, …etc.)</t>
+  </si>
+  <si>
+    <t>A specific, actionable outcome that translates a vision and mission into something to be achieved.</t>
+  </si>
+  <si>
+    <t>Overt or veiled aggression (anger, contempt, or antagonism) directed at others. A red-flag behavior that damages psychological safety and team cohesion.</t>
+  </si>
+  <si>
+    <t>Jokes, teasing, or sarcasm at others' expense, which can mask hostility, belittle and/or offend people, or deflect from real issues. A communication red flag.</t>
+  </si>
+  <si>
+    <t>A measure of cognitive and analytical intelligence and how easily we learn. Distinct from EQ, strong technical IQ does not guarantee the people skills project leadership requires; the two are not directly correlated.</t>
+  </si>
+  <si>
+    <t>The interconnected brain structures involved in processing emotions, forming memories, and shaping motivation and social responses. In the simplified model used in this course, the limbic brain is described as the “emotional brain” to help build self-awareness and understand emotional reactions</t>
+  </si>
+  <si>
+    <t>The outer layer of the brain involved in rational thought, reasoning, language, planning, and conscious decision-making. In the simplified model used in this course, the neocortex is described as the “thinking brain” to help build self-awareness and understand the role of deliberate thought in managing emotional reactions.</t>
+  </si>
+  <si>
+    <t>The brain systems involved in automatic survival functions and instinctive responses, including the regulation of breathing, heart rate, and rapid defensive reactions. In the simplified model used in this course, the old or “reptilian” brain is described as the “survival brain” to help build self-awareness and understand automatic reactions to perceived threats.</t>
+  </si>
+  <si>
+    <t>The indirect expression of negative feelings or resistance through behaviors such as the silent treatment, backhanded comments, deliberate procrastination, or intentional failure to follow through rather than through open communication. It is a red-flag behavior that can be difficult to distinguish from carelessness, forgetfulness, or poor communication, so patterns and context should be considered and assuming intent can be hazardous.</t>
+  </si>
+  <si>
+    <t>A common and significant red-flag behavior in which a person repeatedly presents themselves as powerless or blameless while assigning responsibility to others or to circumstances. This pattern can prevent accountability and block problem-solving. Taking ownership, identifying available choices, and working collaboratively toward solutions are constructive alternatives.</t>
+  </si>
+  <si>
+    <t>Consciously or unconsciously filling in missing information by imagining negative explanations or future outcomes before the facts are known. These imagined scenarios can generate real emotions that affect behavior, performance, and relationships. For example, after a boss says, “We need to meet. See me at 2:00,” an employee may imagine, “I’m in trouble,” “She is angry with me,” or “I’m going to be fired,” then experience anxiety and respond defensively before learning the actual reason for the meeting. Pre-thinking can involve other cognitive distortions, including mind reading, fortune-telling, and catastrophizing.</t>
+  </si>
+  <si>
+    <t>Intentionally imagining that a future situation has already turned out poorly, then reasoning backward to identify what may have caused the undesirable outcome. This helps uncover risks and allows preventive action to be taken now..</t>
+  </si>
+  <si>
+    <t>Responding quickly and automatically to a trigger, with immediate emotions shaping thoughts, words, or actions before the situation has been fully considered. Reactivity is a red flag behavior that can lead to impulsive or unhelpful responses that negatively affect judgment, performance, and relationships.</t>
+  </si>
+  <si>
+    <t>A realistic belief in one’s abilities, judgment, and capacity to learn and adapt. It allows a person to make decisions, take appropriate risks, and act under uncertainty without requiring constant reassurance or projecting arrogance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A goal that is Specific, Measurable, Achievable, Realistic, and Time-bound </t>
+  </si>
+  <si>
+    <t>The foundation of emotional intelligence. It is the ability to notice, accurately identify, and label your emotions, thoughts, triggers, strengths, and limitations, while recognizing how they influence your behavior and affect others in the moment.</t>
+  </si>
+  <si>
+    <t>Vision is the desired future state (what some future point will be like); mission is why and how you'll get there.</t>
+  </si>
+  <si>
+    <t>Interpersonal and self-management capabilities, including communication, empathy, collaboration, leadership, adaptability, and emotional intelligence. These skills complement technical or “hard” skills and are essential to effective performance, teamwork, and project success</t>
+  </si>
+  <si>
+    <t>A set of warning signs of damaging workplace behavior/communication discussed in class (Inappropriate Humor, Sarcasm, Passive-Aggressive Behavior, Hostility, Playing the Victim, Blaming Others, Avoiding or Withdrawing)</t>
+  </si>
+  <si>
+    <t>A class acronym for active/effective listening, a structured reminder of good listening behaviors.(Appreciative, Empathetic, Inquisitive, Open-minded, Understanding)</t>
+  </si>
+  <si>
+    <t>The tendency to attribute others’ failures primarily to factors internal to the agent (such as character, ability, or disposition) while attributing our own failures primarily to external or situational factors</t>
+  </si>
+  <si>
+    <t>Snubbing someone in a social or workplace interaction by paying attention to your phone instead of them.</t>
+  </si>
+  <si>
+    <t>Sympathy involves sharing or feeling concern for another person’s feelings; empathy involves understanding and appreciating another person’s perspective, thoughts, and emotions from their point of view. For project managers, empathy is the more valuable leadership skill. Empathy does not require sympathy or agreement. |</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The use of mocking or ironic remarks to express criticism, anger, frustration, or contempt indirectly, often under the cover of humor. Not all sarcasm is harmful, but </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>any</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sarcasm that is directed at others or used to avoid honest communication can damage trust and is a communication red flag</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -549,9 +535,36 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -604,41 +617,59 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{F5D539A9-57CC-4A1D-95B0-716F1CBFEC56}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -938,791 +969,737 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="94" customWidth="1"/>
-    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32" style="9" customWidth="1"/>
+    <col min="2" max="2" width="94" style="9" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="C1" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B6" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C8" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C9" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="B10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="B12" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="B14" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B15" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="B16" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B18" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B19" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="B20" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B21" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="B22" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B23" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C24" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="B25" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B26" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="B27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C27" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="B28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B29" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="B30" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C30" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="B31" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B32" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="B33" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B34" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="B35" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B36" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    </row>
+    <row r="38" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="B38" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="C39" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="B41" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B42" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="B43" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C43" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B44" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="C44" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B45" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="C45" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B46" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="C46" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B47" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="C47" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B48" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="C48" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B49" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="C49" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B50" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="C50" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B51" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+      <c r="C51" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B52" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+      <c r="C52" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B53" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+      <c r="C53" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B54" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="C54" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B55" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+      <c r="C55" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B56" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C56" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+    <row r="57" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B57" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+      <c r="C57" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="3" t="s">
+    </row>
+    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+      <c r="B58" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C58" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+      <c r="B59" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C59" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="B60" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C60" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+      <c r="B61" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C61" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+      <c r="B62" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C62" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+      <c r="B63" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C63" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+      <c r="B64" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C64" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="B65" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
+      <c r="C65" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="14"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C70" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C65" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1730,96 +1707,96 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>158</v>
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:1" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/pm_glossary.xlsx
+++ b/pm_glossary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbtne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BEB573-70FE-4DFF-8AA4-A69CE054C3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DA3262-0D67-4D7A-BC33-39F891910D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26115" yWindow="1140" windowWidth="27510" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="27510" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Glossary" sheetId="1" r:id="rId1"/>
@@ -374,16 +374,10 @@
     <t>A pair of structures in the limbic system involved in detecting emotionally significant stimuli, especially potential threats, and rapidly coordinating responses before deliberate reasoning fully engages. The amygdala helps initiate fight, flight, or freeze responses to threats,...whether real, perceived, remembered, or imagined. Understanding this process can help project leaders recognize and manage their reactions under pressure.</t>
   </si>
   <si>
-    <t>Why call a Problem an Opportinity or a Challenge?</t>
-  </si>
-  <si>
     <t>For many people and in many situations, the word “problem” can trigger negative emotions or reinforce feelings of powerlessness and defeat. Reframing a problem as an opportunity or challenge can reduce this negative response and encourage a more constructive, solution-oriented mindset.</t>
   </si>
   <si>
     <t>Habitual, involuntary negative interpretations that arise automatically (e.g., “This will never work” or “They think I’m incompetent” or "this meeting will be more wasted time"). Noticing and challenging ANTs is a core emotional self-management skill.</t>
-  </si>
-  <si>
-    <t>A moment, large or small, when stress, frustration, fear, or another emotional trigger disrupts a person’s ability to respond in the most effectuve manner. Breakdowns can occur frequently and may appear as criticism, sarcasm, withdrawal, withholding information, avoiding responsibility, or failing to speak up. Even small breakdowns can impair performance and judgment and damage trust and relationships. Recognizing and managing them early is an important self-management skill.</t>
   </si>
   <si>
     <t>Cognitive Distortions</t>
@@ -501,12 +495,18 @@
       <t xml:space="preserve"> sarcasm that is directed at others or used to avoid honest communication can damage trust and is a communication red flag</t>
     </r>
   </si>
+  <si>
+    <t>Why call a Problem an Opportunity or a Challenge?</t>
+  </si>
+  <si>
+    <t>A moment, large or small, when stress, frustration, fear, or another emotional trigger disrupts a person’s ability to respond in the most effective manner. Breakdowns can occur frequently and may appear as criticism, sarcasm, withdrawal, withholding information, avoiding responsibility, or failing to speak up. Even small breakdowns can impair performance and judgment and damage trust and relationships. Recognizing and managing them early is an important self-management skill.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,13 +533,6 @@
       <color rgb="FFB31B1B"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -619,9 +612,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -632,38 +625,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -972,29 +964,28 @@
   <dimension ref="A1:C66"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32" style="9" customWidth="1"/>
-    <col min="2" max="2" width="94" style="9" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="9"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="94" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1027,7 +1018,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>2</v>
@@ -1038,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>2</v>
@@ -1046,10 +1037,10 @@
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>2</v>
@@ -1082,7 +1073,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>2</v>
@@ -1093,7 +1084,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>2</v>
@@ -1104,7 +1095,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>2</v>
@@ -1115,7 +1106,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>2</v>
@@ -1126,7 +1117,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>2</v>
@@ -1137,7 +1128,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>2</v>
@@ -1147,8 +1138,8 @@
       <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>128</v>
+      <c r="B16" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>2</v>
@@ -1159,7 +1150,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>2</v>
@@ -1170,7 +1161,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>2</v>
@@ -1181,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>2</v>
@@ -1192,7 +1183,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2</v>
@@ -1203,7 +1194,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>2</v>
@@ -1214,7 +1205,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>2</v>
@@ -1225,7 +1216,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>2</v>
@@ -1247,7 +1238,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>2</v>
@@ -1257,8 +1248,8 @@
       <c r="A26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>137</v>
+      <c r="B26" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>2</v>
@@ -1280,7 +1271,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>2</v>
@@ -1291,7 +1282,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>2</v>
@@ -1312,8 +1303,8 @@
       <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>150</v>
+      <c r="B31" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>2</v>
@@ -1324,7 +1315,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>2</v>
@@ -1335,7 +1326,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>2</v>
@@ -1346,7 +1337,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>2</v>
@@ -1356,8 +1347,8 @@
       <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>144</v>
+      <c r="B35" t="s">
+        <v>142</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>2</v>
@@ -1368,7 +1359,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>2</v>
@@ -1379,7 +1370,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>41</v>
@@ -1390,7 +1381,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>41</v>
@@ -1412,7 +1403,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>41</v>
@@ -1423,7 +1414,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>41</v>
@@ -1434,7 +1425,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>41</v>
@@ -1694,9 +1685,9 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="14"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
+      <c r="A66" s="13"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C65" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
